--- a/bdatos_bcie26.xlsx
+++ b/bdatos_bcie26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://minedgob1-my.sharepoint.com/personal/squintanilla_mined_gob_sv/Documents/Escritorio/Visor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\BCIE 2026\Base Datos BCIE 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="14_{0ADD51A1-84E5-490B-9E3B-6F09CC3EC397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C732C581-1F0D-4B0D-85FE-4615EC738EE7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F46FCB2-8BC7-4735-8E8B-5774E69DA7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6600" windowWidth="29040" windowHeight="15840" xr2:uid="{D7D0196A-CB39-4557-81FA-8E4BDE6658BA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D7D0196A-CB39-4557-81FA-8E4BDE6658BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="315">
   <si>
     <t>Grupo</t>
   </si>
@@ -812,9 +812,6 @@
     <t>virtualidad</t>
   </si>
   <si>
-    <t>Reubicado - Retorno</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -852,6 +849,138 @@
   </si>
   <si>
     <t>PEGAS Ejecución</t>
+  </si>
+  <si>
+    <t>Finalizado - CE en uso</t>
+  </si>
+  <si>
+    <t>Finalizado - CE Pendiente</t>
+  </si>
+  <si>
+    <t>CE TRANSITO CIENFUEGOS</t>
+  </si>
+  <si>
+    <t>CE SOLEDAD MORENO DE BENAVIDES</t>
+  </si>
+  <si>
+    <t>CANDELARIA DE LA FRONTERA</t>
+  </si>
+  <si>
+    <t>CE FRANCISCO IGNACIO CORDERO</t>
+  </si>
+  <si>
+    <t>CHALCHUAPA</t>
+  </si>
+  <si>
+    <t>CE CANTON EL PINALON</t>
+  </si>
+  <si>
+    <t>COMP EDUC LOTIFICACION EL ROSARIO CANTON LOS AMATES</t>
+  </si>
+  <si>
+    <t>SAN SEBASTIAN SALITRILLO</t>
+  </si>
+  <si>
+    <t>CE UNION PANAMERICAN</t>
+  </si>
+  <si>
+    <t>MORAZAN</t>
+  </si>
+  <si>
+    <t>PERQUIN</t>
+  </si>
+  <si>
+    <t>CE LIC JUAN JOSE GUZMAN</t>
+  </si>
+  <si>
+    <t>SAN CARLOS</t>
+  </si>
+  <si>
+    <t>COMP EDUC JOSE PANTOJA HIJO</t>
+  </si>
+  <si>
+    <t>LA UNION, URBANA</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR BARRIO LA FATIMA</t>
+  </si>
+  <si>
+    <t>CE REPUBLICA DE HONDURAS</t>
+  </si>
+  <si>
+    <t>CE MIGUEL CABRERA</t>
+  </si>
+  <si>
+    <t>AGUA CALIENTE</t>
+  </si>
+  <si>
+    <t>CE BARRIO EL CENTRO</t>
+  </si>
+  <si>
+    <t>NUEVA CONCEPCION</t>
+  </si>
+  <si>
+    <t>CE JOSE MARTI</t>
+  </si>
+  <si>
+    <t>SAN IGNACIO</t>
+  </si>
+  <si>
+    <t>CE CASERIO LAS LAJAS</t>
+  </si>
+  <si>
+    <t>CE SAN LUIS DE LA REINA</t>
+  </si>
+  <si>
+    <t>SAN LUIS DE LA REINA</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR DOCTOR MANUEL QUIJANO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SESORI</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR ALBERTO MENJIVAR RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VICTORIA, URBANA</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR CANTON EL CIMARRON</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR DE TEOTEPEQUE</t>
+  </si>
+  <si>
+    <t>TEOTEPEQUE</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR URBANIZACION MONTELIMAR</t>
+  </si>
+  <si>
+    <t>OLOCUILTA</t>
+  </si>
+  <si>
+    <t>COMPLEJO EDUCATIVO PROFESOR REYNALDO PADILLA</t>
+  </si>
+  <si>
+    <t>COMPLEJO EDUCATIVO ANGELINA ANGEL PANAMEÑO</t>
+  </si>
+  <si>
+    <t>CUSCATLAN</t>
+  </si>
+  <si>
+    <t>EL CARMEN</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR SAN AGUSTIN</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR PROFESOR JUAN ROBERTO JUAREZ</t>
+  </si>
+  <si>
+    <t>CENTRO ESCOLAR CANTON TIERRA BLANCA</t>
   </si>
 </sst>
 </file>
@@ -961,10 +1090,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A247F66-7F64-4F5B-BD9F-527C7E35E6CC}">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.77734375" style="7" bestFit="1" customWidth="1"/>
@@ -1319,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
@@ -1334,28 +1459,28 @@
         <v>2</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>250</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>251</v>
@@ -1396,7 +1521,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>245</v>
@@ -1417,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1452,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>245</v>
@@ -1473,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1529,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1585,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1641,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1697,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1732,7 +1857,7 @@
         <v>17</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>245</v>
@@ -1753,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1788,7 +1913,7 @@
         <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>245</v>
@@ -1809,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1844,7 +1969,7 @@
         <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>245</v>
@@ -1865,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1900,7 +2025,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>37</v>
@@ -1956,7 +2081,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>37</v>
@@ -1965,7 +2090,7 @@
         <v>38</v>
       </c>
       <c r="N12" s="8">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>10</v>
@@ -2012,7 +2137,7 @@
         <v>36</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>37</v>
@@ -2021,7 +2146,7 @@
         <v>38</v>
       </c>
       <c r="N13" s="8">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>10</v>
@@ -2077,7 +2202,7 @@
         <v>38</v>
       </c>
       <c r="N14" s="8">
-        <v>0.78100000000000003</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>10</v>
@@ -2133,7 +2258,7 @@
         <v>38</v>
       </c>
       <c r="N15" s="8">
-        <v>0.60299999999999998</v>
+        <v>0.60340000000000005</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>10</v>
@@ -2180,7 +2305,7 @@
         <v>49</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>245</v>
@@ -2201,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2236,7 +2361,7 @@
         <v>49</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>245</v>
@@ -2257,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2292,7 +2417,7 @@
         <v>49</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>55</v>
@@ -2301,7 +2426,7 @@
         <v>38</v>
       </c>
       <c r="N18" s="8">
-        <v>0.98699999999999999</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>10</v>
@@ -2357,7 +2482,7 @@
         <v>38</v>
       </c>
       <c r="N19" s="8">
-        <v>0.38640000000000002</v>
+        <v>0.39150000000000001</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>10</v>
@@ -2413,7 +2538,7 @@
         <v>38</v>
       </c>
       <c r="N20" s="8">
-        <v>0.32090000000000002</v>
+        <v>0.33</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>10</v>
@@ -2469,7 +2594,7 @@
         <v>38</v>
       </c>
       <c r="N21" s="8">
-        <v>0.31919999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>10</v>
@@ -2525,7 +2650,7 @@
         <v>38</v>
       </c>
       <c r="N22" s="8">
-        <v>0.51500000000000001</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>10</v>
@@ -2581,7 +2706,7 @@
         <v>38</v>
       </c>
       <c r="N23" s="8">
-        <v>0.63600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>10</v>
@@ -2637,7 +2762,7 @@
         <v>38</v>
       </c>
       <c r="N24" s="8">
-        <v>0.53100000000000003</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>10</v>
@@ -2693,7 +2818,7 @@
         <v>38</v>
       </c>
       <c r="N25" s="8">
-        <v>0.51900000000000002</v>
+        <v>0.59</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>10</v>
@@ -2749,7 +2874,7 @@
         <v>38</v>
       </c>
       <c r="N26" s="8">
-        <v>0.75600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>10</v>
@@ -2805,7 +2930,7 @@
         <v>38</v>
       </c>
       <c r="N27" s="8">
-        <v>0.60499999999999998</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>10</v>
@@ -2861,7 +2986,7 @@
         <v>38</v>
       </c>
       <c r="N28" s="8">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>10</v>
@@ -2908,7 +3033,7 @@
         <v>230</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>80</v>
@@ -2964,7 +3089,7 @@
         <v>230</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>85</v>
@@ -3020,7 +3145,7 @@
         <v>230</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>80</v>
@@ -3076,7 +3201,7 @@
         <v>230</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>85</v>
@@ -3132,7 +3257,7 @@
         <v>230</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>85</v>
@@ -3188,7 +3313,7 @@
         <v>94</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>80</v>
@@ -3197,7 +3322,7 @@
         <v>38</v>
       </c>
       <c r="N34" s="8">
-        <v>0.22</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>10</v>
@@ -3692,7 +3817,7 @@
         <v>233</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>113</v>
@@ -3748,7 +3873,7 @@
         <v>233</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>113</v>
@@ -3916,7 +4041,7 @@
         <v>235</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>113</v>
@@ -3925,7 +4050,7 @@
         <v>38</v>
       </c>
       <c r="N47" s="8">
-        <v>2.58E-2</v>
+        <v>0.19539999999999999</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>10</v>
@@ -3972,7 +4097,7 @@
         <v>235</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>113</v>
@@ -3981,7 +4106,7 @@
         <v>38</v>
       </c>
       <c r="N48" s="8">
-        <v>2.1600000000000001E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>10</v>
@@ -4028,7 +4153,7 @@
         <v>236</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>121</v>
@@ -4084,7 +4209,7 @@
         <v>236</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>121</v>
@@ -4140,7 +4265,7 @@
         <v>236</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>121</v>
@@ -4196,7 +4321,7 @@
         <v>236</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>121</v>
@@ -4252,7 +4377,7 @@
         <v>237</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>55</v>
@@ -4364,7 +4489,7 @@
         <v>238</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>143</v>
@@ -4429,7 +4554,7 @@
         <v>38</v>
       </c>
       <c r="N56" s="8">
-        <v>2E-3</v>
+        <v>3.5299999999999998E-2</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>10</v>
@@ -4485,7 +4610,7 @@
         <v>38</v>
       </c>
       <c r="N57" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>10</v>
@@ -4541,7 +4666,7 @@
         <v>38</v>
       </c>
       <c r="N58" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>10</v>
@@ -4812,7 +4937,7 @@
         <v>162</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>37</v>
@@ -4821,7 +4946,7 @@
         <v>38</v>
       </c>
       <c r="N63" s="8">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>10</v>
@@ -4877,7 +5002,7 @@
         <v>38</v>
       </c>
       <c r="N64" s="8">
-        <v>0</v>
+        <v>4.99E-2</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>10</v>
@@ -4933,7 +5058,7 @@
         <v>38</v>
       </c>
       <c r="N65" s="8">
-        <v>0</v>
+        <v>4.6800000000000001E-2</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>10</v>
@@ -4980,7 +5105,7 @@
         <v>165</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>85</v>
@@ -4989,7 +5114,7 @@
         <v>38</v>
       </c>
       <c r="N66" s="8">
-        <v>1.9E-2</v>
+        <v>2.98E-2</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>10</v>
@@ -5036,7 +5161,7 @@
         <v>171</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>172</v>
@@ -5044,9 +5169,7 @@
       <c r="M67" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="N67" s="8">
-        <v>0</v>
-      </c>
+      <c r="N67" s="8"/>
       <c r="O67" s="2" t="s">
         <v>82</v>
       </c>
@@ -5157,7 +5280,7 @@
         <v>38</v>
       </c>
       <c r="N69" s="8">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>10</v>
@@ -5428,7 +5551,7 @@
         <v>186</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>245</v>
@@ -5436,9 +5559,7 @@
       <c r="M74" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N74" s="8">
-        <v>0</v>
-      </c>
+      <c r="N74" s="8"/>
       <c r="O74" s="2" t="s">
         <v>10</v>
       </c>
@@ -5484,7 +5605,7 @@
         <v>186</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>245</v>
@@ -5492,9 +5613,7 @@
       <c r="M75" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N75" s="8">
-        <v>0</v>
-      </c>
+      <c r="N75" s="8"/>
       <c r="O75" s="2" t="s">
         <v>10</v>
       </c>
@@ -5540,7 +5659,7 @@
         <v>186</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>245</v>
@@ -5548,9 +5667,7 @@
       <c r="M76" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N76" s="8">
-        <v>0</v>
-      </c>
+      <c r="N76" s="8"/>
       <c r="O76" s="2" t="s">
         <v>10</v>
       </c>
@@ -5596,7 +5713,7 @@
         <v>186</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>245</v>
@@ -5604,9 +5721,7 @@
       <c r="M77" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N77" s="8">
-        <v>0</v>
-      </c>
+      <c r="N77" s="8"/>
       <c r="O77" s="2" t="s">
         <v>10</v>
       </c>
@@ -5652,7 +5767,7 @@
         <v>186</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>245</v>
@@ -5660,9 +5775,7 @@
       <c r="M78" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N78" s="8">
-        <v>0</v>
-      </c>
+      <c r="N78" s="8"/>
       <c r="O78" s="2" t="s">
         <v>10</v>
       </c>
@@ -5708,7 +5821,7 @@
         <v>186</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>245</v>
@@ -5716,9 +5829,7 @@
       <c r="M79" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N79" s="8">
-        <v>0</v>
-      </c>
+      <c r="N79" s="8"/>
       <c r="O79" s="2" t="s">
         <v>10</v>
       </c>
@@ -5764,7 +5875,7 @@
         <v>186</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>245</v>
@@ -5772,9 +5883,7 @@
       <c r="M80" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N80" s="8">
-        <v>0</v>
-      </c>
+      <c r="N80" s="8"/>
       <c r="O80" s="2" t="s">
         <v>10</v>
       </c>
@@ -5820,7 +5929,7 @@
         <v>186</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>245</v>
@@ -5828,9 +5937,7 @@
       <c r="M81" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="N81" s="8">
-        <v>0</v>
-      </c>
+      <c r="N81" s="8"/>
       <c r="O81" s="2" t="s">
         <v>10</v>
       </c>
@@ -5885,7 +5992,7 @@
         <v>38</v>
       </c>
       <c r="N82" s="8">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>10</v>
@@ -5941,7 +6048,7 @@
         <v>38</v>
       </c>
       <c r="N83" s="8">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>10</v>
@@ -5997,7 +6104,7 @@
         <v>38</v>
       </c>
       <c r="N84" s="8">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>10</v>
@@ -6053,7 +6160,7 @@
         <v>38</v>
       </c>
       <c r="N85" s="8">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>10</v>
@@ -6109,7 +6216,7 @@
         <v>38</v>
       </c>
       <c r="N86" s="8">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>10</v>
@@ -6156,7 +6263,7 @@
         <v>200</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>201</v>
@@ -6165,7 +6272,7 @@
         <v>38</v>
       </c>
       <c r="N87" s="8">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>10</v>
@@ -6208,9 +6315,11 @@
       <c r="I88" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J88" s="4"/>
+      <c r="J88" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K88" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>245</v>
@@ -6262,9 +6371,11 @@
       <c r="I89" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J89" s="4"/>
+      <c r="J89" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K89" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>245</v>
@@ -6316,7 +6427,9 @@
       <c r="I90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J90" s="4"/>
+      <c r="J90" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K90" s="2" t="s">
         <v>153</v>
       </c>
@@ -6324,11 +6437,9 @@
         <v>245</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N90" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N90" s="8"/>
       <c r="O90" s="2" t="s">
         <v>10</v>
       </c>
@@ -6370,19 +6481,19 @@
       <c r="I91" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J91" s="4"/>
+      <c r="J91" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K91" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N91" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N91" s="8"/>
       <c r="O91" s="2" t="s">
         <v>10</v>
       </c>
@@ -6424,19 +6535,19 @@
       <c r="I92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J92" s="4"/>
+      <c r="J92" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K92" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N92" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N92" s="8"/>
       <c r="O92" s="2" t="s">
         <v>10</v>
       </c>
@@ -6478,19 +6589,19 @@
       <c r="I93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J93" s="4"/>
+      <c r="J93" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K93" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N93" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N93" s="8"/>
       <c r="O93" s="2" t="s">
         <v>10</v>
       </c>
@@ -6532,7 +6643,9 @@
       <c r="I94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J94" s="4"/>
+      <c r="J94" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K94" s="2" t="s">
         <v>108</v>
       </c>
@@ -6540,11 +6653,9 @@
         <v>245</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N94" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N94" s="8"/>
       <c r="O94" s="2" t="s">
         <v>10</v>
       </c>
@@ -6586,19 +6697,19 @@
       <c r="I95" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J95" s="4"/>
+      <c r="J95" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K95" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N95" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N95" s="8"/>
       <c r="O95" s="2" t="s">
         <v>10</v>
       </c>
@@ -6640,19 +6751,19 @@
       <c r="I96" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J96" s="4"/>
+      <c r="J96" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K96" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N96" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N96" s="8"/>
       <c r="O96" s="2" t="s">
         <v>10</v>
       </c>
@@ -6694,19 +6805,19 @@
       <c r="I97" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J97" s="4"/>
+      <c r="J97" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K97" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N97" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N97" s="8"/>
       <c r="O97" s="2" t="s">
         <v>10</v>
       </c>
@@ -6748,19 +6859,19 @@
       <c r="I98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J98" s="4"/>
+      <c r="J98" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K98" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>245</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="N98" s="8">
-        <v>1</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N98" s="8"/>
       <c r="O98" s="2" t="s">
         <v>10</v>
       </c>
@@ -6802,9 +6913,11 @@
       <c r="I99" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J99" s="4"/>
+      <c r="J99" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K99" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>245</v>
@@ -6856,9 +6969,11 @@
       <c r="I100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J100" s="4"/>
+      <c r="J100" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K100" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>245</v>
@@ -6910,9 +7025,11 @@
       <c r="I101" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J101" s="4"/>
+      <c r="J101" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K101" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>245</v>
@@ -6964,7 +7081,9 @@
       <c r="I102" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J102" s="4"/>
+      <c r="J102" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K102" s="2" t="s">
         <v>108</v>
       </c>
@@ -7018,9 +7137,11 @@
       <c r="I103" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J103" s="4"/>
+      <c r="J103" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K103" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>245</v>
@@ -7072,9 +7193,11 @@
       <c r="I104" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J104" s="4"/>
+      <c r="J104" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="K104" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>245</v>
@@ -7096,6 +7219,1406 @@
       </c>
       <c r="R104" s="3" t="s">
         <v>255</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>-89.53197222</v>
+      </c>
+      <c r="B105" s="3">
+        <v>13.967000000000001</v>
+      </c>
+      <c r="C105" s="2">
+        <v>10</v>
+      </c>
+      <c r="D105" s="2">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2">
+        <v>10429</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N105" s="8">
+        <v>0</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R105" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>-89.649722220000001</v>
+      </c>
+      <c r="B106" s="3">
+        <v>14.11238889</v>
+      </c>
+      <c r="C106" s="2">
+        <v>10</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2">
+        <v>10198</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N106" s="8">
+        <v>0</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R106" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>-89.675333330000001</v>
+      </c>
+      <c r="B107" s="3">
+        <v>13.98366667</v>
+      </c>
+      <c r="C107" s="2">
+        <v>10</v>
+      </c>
+      <c r="D107" s="2">
+        <v>3</v>
+      </c>
+      <c r="E107" s="2">
+        <v>10268</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N107" s="8">
+        <v>0</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R107" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>-89.559972220000006</v>
+      </c>
+      <c r="B108" s="3">
+        <v>14.10125</v>
+      </c>
+      <c r="C108" s="2">
+        <v>10</v>
+      </c>
+      <c r="D108" s="2">
+        <v>4</v>
+      </c>
+      <c r="E108" s="2">
+        <v>10455</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N108" s="8">
+        <v>0</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>-89.646249999999995</v>
+      </c>
+      <c r="B109" s="3">
+        <v>13.99775</v>
+      </c>
+      <c r="C109" s="2">
+        <v>10</v>
+      </c>
+      <c r="D109" s="2">
+        <v>5</v>
+      </c>
+      <c r="E109" s="2">
+        <v>86287</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N109" s="8">
+        <v>0</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>-89.183611110000001</v>
+      </c>
+      <c r="B110" s="3">
+        <v>13.681944440000001</v>
+      </c>
+      <c r="C110" s="2">
+        <v>10</v>
+      </c>
+      <c r="D110" s="2">
+        <v>6</v>
+      </c>
+      <c r="E110" s="2">
+        <v>13242</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N110" s="8">
+        <v>0</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>-88.092916669999994</v>
+      </c>
+      <c r="B111" s="3">
+        <v>13.64777778</v>
+      </c>
+      <c r="C111" s="2">
+        <v>10</v>
+      </c>
+      <c r="D111" s="2">
+        <v>7</v>
+      </c>
+      <c r="E111" s="2">
+        <v>13249</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N111" s="8">
+        <v>0</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>-87.843944440000001</v>
+      </c>
+      <c r="B112" s="3">
+        <v>13.33897222</v>
+      </c>
+      <c r="C112" s="2">
+        <v>10</v>
+      </c>
+      <c r="D112" s="2">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2">
+        <v>13443</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N112" s="8">
+        <v>0</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R112" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>-87.843000000000004</v>
+      </c>
+      <c r="B113" s="3">
+        <v>13.332916669999999</v>
+      </c>
+      <c r="C113" s="2">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2">
+        <v>9</v>
+      </c>
+      <c r="E113" s="2">
+        <v>13446</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N113" s="8">
+        <v>0</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>-87.854277780000004</v>
+      </c>
+      <c r="B114" s="3">
+        <v>13.34055556</v>
+      </c>
+      <c r="C114" s="2">
+        <v>10</v>
+      </c>
+      <c r="D114" s="2">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2">
+        <v>10820</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N114" s="8">
+        <v>0</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R114" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>-89.233055559999997</v>
+      </c>
+      <c r="B115" s="3">
+        <v>14.180277780000001</v>
+      </c>
+      <c r="C115" s="2">
+        <v>10</v>
+      </c>
+      <c r="D115" s="2">
+        <v>11</v>
+      </c>
+      <c r="E115" s="2">
+        <v>10756</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N115" s="8">
+        <v>0</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>-89.293888890000005</v>
+      </c>
+      <c r="B116" s="3">
+        <v>14.123333329999999</v>
+      </c>
+      <c r="C116" s="2">
+        <v>10</v>
+      </c>
+      <c r="D116" s="2">
+        <v>12</v>
+      </c>
+      <c r="E116" s="2">
+        <v>10915</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N116" s="8">
+        <v>0</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R116" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>-89.180444440000002</v>
+      </c>
+      <c r="B117" s="3">
+        <v>14.33997222</v>
+      </c>
+      <c r="C117" s="2">
+        <v>10</v>
+      </c>
+      <c r="D117" s="2">
+        <v>13</v>
+      </c>
+      <c r="E117" s="2">
+        <v>10949</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N117" s="8">
+        <v>0</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R117" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>-89.577833330000004</v>
+      </c>
+      <c r="B118" s="3">
+        <v>13.81588889</v>
+      </c>
+      <c r="C118" s="2">
+        <v>10</v>
+      </c>
+      <c r="D118" s="2">
+        <v>14</v>
+      </c>
+      <c r="E118" s="2">
+        <v>82062</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N118" s="8">
+        <v>0</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P118" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R118" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>-88.344305559999995</v>
+      </c>
+      <c r="B119" s="3">
+        <v>13.81497222</v>
+      </c>
+      <c r="C119" s="2">
+        <v>10</v>
+      </c>
+      <c r="D119" s="2">
+        <v>15</v>
+      </c>
+      <c r="E119" s="2">
+        <v>12975</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N119" s="8">
+        <v>0</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>-88.361166670000003</v>
+      </c>
+      <c r="B120" s="3">
+        <v>13.717499999999999</v>
+      </c>
+      <c r="C120" s="2">
+        <v>10</v>
+      </c>
+      <c r="D120" s="2">
+        <v>16</v>
+      </c>
+      <c r="E120" s="2">
+        <v>13122</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N120" s="8">
+        <v>0</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>-88.632541669999995</v>
+      </c>
+      <c r="B121" s="3">
+        <v>13.945966670000001</v>
+      </c>
+      <c r="C121" s="2">
+        <v>10</v>
+      </c>
+      <c r="D121" s="2">
+        <v>17</v>
+      </c>
+      <c r="E121" s="2">
+        <v>12294</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N121" s="8">
+        <v>0</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q121" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>-89.297777780000004</v>
+      </c>
+      <c r="B122" s="3">
+        <v>13.53055556</v>
+      </c>
+      <c r="C122" s="2">
+        <v>10</v>
+      </c>
+      <c r="D122" s="2">
+        <v>18</v>
+      </c>
+      <c r="E122" s="2">
+        <v>11095</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N122" s="8">
+        <v>0</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q122" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R122" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>-89.518611109999995</v>
+      </c>
+      <c r="B123" s="3">
+        <v>13.59055556</v>
+      </c>
+      <c r="C123" s="2">
+        <v>10</v>
+      </c>
+      <c r="D123" s="2">
+        <v>19</v>
+      </c>
+      <c r="E123" s="2">
+        <v>11284</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N123" s="8">
+        <v>0</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>-89.122777780000007</v>
+      </c>
+      <c r="B124" s="3">
+        <v>13.598055560000001</v>
+      </c>
+      <c r="C124" s="2">
+        <v>10</v>
+      </c>
+      <c r="D124" s="2">
+        <v>20</v>
+      </c>
+      <c r="E124" s="2">
+        <v>10084</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N124" s="8">
+        <v>0</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q124" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>-88.916555560000006</v>
+      </c>
+      <c r="B125" s="3">
+        <v>13.305944439999999</v>
+      </c>
+      <c r="C125" s="2">
+        <v>10</v>
+      </c>
+      <c r="D125" s="2">
+        <v>21</v>
+      </c>
+      <c r="E125" s="2">
+        <v>12132</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N125" s="8">
+        <v>0</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>-88.913055560000004</v>
+      </c>
+      <c r="B126" s="3">
+        <v>13.75111111</v>
+      </c>
+      <c r="C126" s="2">
+        <v>10</v>
+      </c>
+      <c r="D126" s="2">
+        <v>22</v>
+      </c>
+      <c r="E126" s="2">
+        <v>11816</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J126" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N126" s="8">
+        <v>0</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q126" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R126" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>-88.869229869999998</v>
+      </c>
+      <c r="B127" s="3">
+        <v>13.50435055</v>
+      </c>
+      <c r="C127" s="2">
+        <v>10</v>
+      </c>
+      <c r="D127" s="2">
+        <v>23</v>
+      </c>
+      <c r="E127" s="2">
+        <v>12116</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N127" s="8">
+        <v>0</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q127" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R127" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>-88.856166669999993</v>
+      </c>
+      <c r="B128" s="3">
+        <v>13.84333333</v>
+      </c>
+      <c r="C128" s="2">
+        <v>10</v>
+      </c>
+      <c r="D128" s="2">
+        <v>24</v>
+      </c>
+      <c r="E128" s="2">
+        <v>12157</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J128" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N128" s="8">
+        <v>0</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P128" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q128" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R128" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>-88.884027779999997</v>
+      </c>
+      <c r="B129" s="3">
+        <v>13.455083330000001</v>
+      </c>
+      <c r="C129" s="2">
+        <v>10</v>
+      </c>
+      <c r="D129" s="2">
+        <v>25</v>
+      </c>
+      <c r="E129" s="2">
+        <v>12115</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N129" s="8">
+        <v>0</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P129" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q129" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R129" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/bdatos_bcie26.xlsx
+++ b/bdatos_bcie26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\BCIE 2026\Base Datos BCIE 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F46FCB2-8BC7-4735-8E8B-5774E69DA7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B80759-04DA-415B-A85C-9F4D3D5B7F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D7D0196A-CB39-4557-81FA-8E4BDE6658BA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="280">
   <si>
     <t>Grupo</t>
   </si>
@@ -323,9 +323,6 @@
     <t>13/2024</t>
   </si>
   <si>
-    <t>CENTRO ESCOLAR EL CONGO</t>
-  </si>
-  <si>
     <t>EL CONGO</t>
   </si>
   <si>
@@ -335,21 +332,6 @@
     <t>SIN ADJUDICAR</t>
   </si>
   <si>
-    <t>COMPLEJO EDUCATIVO "CAPITÁN GENERAL GERARDO BARRIOS"</t>
-  </si>
-  <si>
-    <t>COATEPEQUE</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR "ARTURO AMBROGI"</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR "JOSÉ DOLORES LARREYNAGA"</t>
-  </si>
-  <si>
-    <t>QUEZALTEPEQUE</t>
-  </si>
-  <si>
     <t>CENTRO ESCOLAR "PONCIANA RAMIREZ"</t>
   </si>
   <si>
@@ -545,18 +527,12 @@
     <t>CENTRO ESCOLAR CIUDAD JARDÍN Nº 3</t>
   </si>
   <si>
-    <t>COMPLEJO EDUCATIVO BARTOLOME BOLAÑOS</t>
-  </si>
-  <si>
     <t>IZALCO</t>
   </si>
   <si>
     <t>26/2024</t>
   </si>
   <si>
-    <t>Eliminada</t>
-  </si>
-  <si>
     <t>CENTRO ESCOLAR VALLE EL CARMEN CANTÓN NATIVIDAD</t>
   </si>
   <si>
@@ -590,48 +566,6 @@
     <t>APCA CONSTRUCCIONES BOBURG</t>
   </si>
   <si>
-    <t>CENTRO ESCOLAR CASERÍO POTRERILLOS, CANTÓN SAN FRANCISCO IRAHETA</t>
-  </si>
-  <si>
-    <t>UDP GYPSA-SERVENCO</t>
-  </si>
-  <si>
-    <t>15/2025</t>
-  </si>
-  <si>
-    <t>Contrato Resindido</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CANTÓN LAS HUERTAS</t>
-  </si>
-  <si>
-    <t>COMPLEJO EDUCATIVO CASERÍO HUISCOYOL, CANTÓN LA TRINIDAD</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO SANTA LUCIA, CANTÓN LAS LOMITAS</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO EL ALTO, CANTÓN HUERTAS VIEJAS</t>
-  </si>
-  <si>
-    <t>ANAMOROS</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CANTON CORRALITO</t>
-  </si>
-  <si>
-    <t>CORINTO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO LLANO GRANDE, CANTÓN CORRALITO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO COPANTE, CANTÓN ESTANCIA</t>
-  </si>
-  <si>
-    <t>CACAOPERA</t>
-  </si>
-  <si>
     <t>CENTRO ESCOLAR CANTÓN LOS APOYOS</t>
   </si>
   <si>
@@ -668,39 +602,9 @@
     <t>COMPLEJO EDUCATIVO CASERÍO RANCHO QUEMADO, CANTÓN MAQUILISHUAT</t>
   </si>
   <si>
-    <t>CENTRO ESCOLAR CASERÍO TACACHICO, CANTÓN TACACHICO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CANTÓN CEIBA DEL CHARCO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO COLONIA LA COLINA, CANTÓN EL ROSARIO</t>
-  </si>
-  <si>
-    <t>COMPLEJO EDUCATIVO CATALINO AMAYA</t>
-  </si>
-  <si>
-    <t>NUEVA ESPARTA</t>
-  </si>
-  <si>
-    <t>COMPLEJO EDUCATIVO CANTÓN EL JOBO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CANTÓN EL SUNZA</t>
-  </si>
-  <si>
     <t>ACAJUTLA</t>
   </si>
   <si>
-    <t>CENTRO ESCOLAR BERND GRABS</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CASERÍO CHAPARRASTIQUE, CANTÓN EL NIÑO</t>
-  </si>
-  <si>
-    <t>CENTRO ESCOLAR CANTÓN TULIMA</t>
-  </si>
-  <si>
     <t>CENTRO ESCOLAR CASERIO COLONIA ARTURO ARMANDO MOLINA, CANTON EL EDEN</t>
   </si>
   <si>
@@ -731,9 +635,6 @@
     <t>11/2024</t>
   </si>
   <si>
-    <t>05/2025</t>
-  </si>
-  <si>
     <t>02/2025</t>
   </si>
   <si>
@@ -777,12 +678,6 @@
   </si>
   <si>
     <t>Ejecutandose</t>
-  </si>
-  <si>
-    <t>Eliminado</t>
-  </si>
-  <si>
-    <t>Sin ejecutar</t>
   </si>
   <si>
     <t>Pendiente</t>
@@ -1409,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A247F66-7F64-4F5B-BD9F-527C7E35E6CC}">
-  <dimension ref="A1:R129"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.77734375" style="7" bestFit="1" customWidth="1"/>
@@ -1435,58 +1330,58 @@
   <sheetData>
     <row r="1" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1521,10 +1416,10 @@
         <v>8</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>9</v>
@@ -1542,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1577,10 +1472,10 @@
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>9</v>
@@ -1598,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1636,7 +1531,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>9</v>
@@ -1654,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1692,7 +1587,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>9</v>
@@ -1710,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1748,7 +1643,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>9</v>
@@ -1766,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1804,7 +1699,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
@@ -1822,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,10 +1752,10 @@
         <v>17</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
@@ -1878,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1913,10 +1808,10 @@
         <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>9</v>
@@ -1934,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1969,10 +1864,10 @@
         <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
@@ -1990,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2025,7 +1920,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>37</v>
@@ -2040,13 +1935,13 @@
         <v>10</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q11" s="12">
         <v>0</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2081,7 +1976,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>37</v>
@@ -2096,13 +1991,13 @@
         <v>10</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q12" s="12">
         <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2137,7 +2032,7 @@
         <v>36</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>37</v>
@@ -2152,13 +2047,13 @@
         <v>10</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q13" s="12">
         <v>0</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2208,13 +2103,13 @@
         <v>10</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q14" s="12">
         <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2264,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q15" s="12">
         <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2305,10 +2200,10 @@
         <v>49</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>9</v>
@@ -2326,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2361,10 +2256,10 @@
         <v>49</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>9</v>
@@ -2382,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2417,7 +2312,7 @@
         <v>49</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>55</v>
@@ -2432,13 +2327,13 @@
         <v>10</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q18" s="12">
         <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2488,13 +2383,13 @@
         <v>10</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q19" s="12">
         <v>0</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2544,13 +2439,13 @@
         <v>10</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q20" s="12">
         <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2600,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q21" s="12">
         <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2656,13 +2551,13 @@
         <v>10</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q22" s="12">
         <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2712,13 +2607,13 @@
         <v>10</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q23" s="12">
         <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2768,13 +2663,13 @@
         <v>10</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q24" s="12">
         <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2824,13 +2719,13 @@
         <v>10</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q25" s="12">
         <v>0</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2880,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q26" s="12">
         <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2936,13 +2831,13 @@
         <v>10</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q27" s="12">
         <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2992,13 +2887,13 @@
         <v>10</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q28" s="12">
         <v>0</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3030,10 +2925,10 @@
         <v>79</v>
       </c>
       <c r="J29" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>80</v>
@@ -3048,13 +2943,13 @@
         <v>82</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q29" s="12">
         <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3086,10 +2981,10 @@
         <v>79</v>
       </c>
       <c r="J30" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>85</v>
@@ -3104,13 +2999,13 @@
         <v>82</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q30" s="12">
         <v>0</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3142,10 +3037,10 @@
         <v>79</v>
       </c>
       <c r="J31" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>80</v>
@@ -3160,13 +3055,13 @@
         <v>82</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q31" s="12">
         <v>0</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,10 +3093,10 @@
         <v>79</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>85</v>
@@ -3216,13 +3111,13 @@
         <v>82</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q32" s="12">
         <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3254,10 +3149,10 @@
         <v>79</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>85</v>
@@ -3272,13 +3167,13 @@
         <v>92</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q33" s="12">
         <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -3313,7 +3208,7 @@
         <v>94</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>80</v>
@@ -3328,2668 +3223,2686 @@
         <v>10</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q34" s="12">
         <v>0</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>13.90583333</v>
+        <v>14.17305556</v>
       </c>
       <c r="B35" s="3">
-        <v>-89.494555559999995</v>
+        <v>-89.105000000000004</v>
       </c>
       <c r="C35" s="2">
         <v>3</v>
       </c>
       <c r="D35" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2">
-        <v>10284</v>
+        <v>10994</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N35" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q35" s="12">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>13.92925</v>
+        <v>13.99994444</v>
       </c>
       <c r="B36" s="3">
-        <v>-89.502777780000002</v>
+        <v>-89.543722220000006</v>
       </c>
       <c r="C36" s="2">
         <v>3</v>
       </c>
       <c r="D36" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2">
-        <v>10220</v>
+        <v>10408</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="N36" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q36" s="12">
         <v>0</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>13.72361111</v>
+        <v>13.755694439999999</v>
       </c>
       <c r="B37" s="3">
-        <v>-89.367500000000007</v>
+        <v>-88.949944439999996</v>
       </c>
       <c r="C37" s="2">
         <v>3</v>
       </c>
       <c r="D37" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2">
-        <v>11032</v>
+        <v>11824</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N37" s="8">
-        <v>0</v>
+        <v>0.89510000000000001</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q37" s="12">
         <v>0</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>13.830555560000001</v>
+        <v>13.81611111</v>
       </c>
       <c r="B38" s="3">
-        <v>-89.272499999999994</v>
+        <v>-89.056944439999995</v>
       </c>
       <c r="C38" s="2">
         <v>3</v>
       </c>
       <c r="D38" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2">
-        <v>11171</v>
+        <v>11827</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N38" s="8">
-        <v>0</v>
+        <v>0.89510000000000001</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q38" s="12">
         <v>0</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>14.17305556</v>
+        <v>13.72138889</v>
       </c>
       <c r="B39" s="3">
-        <v>-89.105000000000004</v>
+        <v>-88.935555559999997</v>
       </c>
       <c r="C39" s="2">
         <v>3</v>
       </c>
       <c r="D39" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2">
-        <v>10994</v>
+        <v>11809</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N39" s="8">
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q39" s="12">
         <v>0</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>13.99994444</v>
+        <v>13.60147222</v>
       </c>
       <c r="B40" s="3">
-        <v>-89.543722220000006</v>
+        <v>-88.926611109999996</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
       </c>
       <c r="D40" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2">
-        <v>10408</v>
+        <v>12024</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="I40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J40" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="M40" s="2" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="N40" s="8">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q40" s="12">
         <v>0</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>13.755694439999999</v>
+        <v>13.909750000000001</v>
       </c>
       <c r="B41" s="3">
-        <v>-88.949944439999996</v>
+        <v>-89.493305559999996</v>
       </c>
       <c r="C41" s="2">
         <v>3</v>
       </c>
       <c r="D41" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2">
-        <v>11824</v>
+        <v>10221</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N41" s="8">
-        <v>0.89510000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q41" s="12">
         <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>13.81611111</v>
+        <v>14.02502778</v>
       </c>
       <c r="B42" s="3">
-        <v>-89.056944439999995</v>
+        <v>-89.524361110000001</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
       </c>
       <c r="D42" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2">
-        <v>11827</v>
+        <v>10428</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="J42" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N42" s="8">
-        <v>0.89510000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q42" s="12">
         <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>13.72138889</v>
+        <v>13.80019444</v>
       </c>
       <c r="B43" s="3">
-        <v>-88.935555559999997</v>
+        <v>-88.154722219999996</v>
       </c>
       <c r="C43" s="2">
         <v>3</v>
       </c>
       <c r="D43" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E43" s="2">
-        <v>11809</v>
+        <v>13241</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N43" s="8">
-        <v>0.56000000000000005</v>
+        <v>0.19539999999999999</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q43" s="12">
         <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>13.60147222</v>
+        <v>13.90694444</v>
       </c>
       <c r="B44" s="3">
-        <v>-88.926611109999996</v>
+        <v>-88.157777780000004</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
       </c>
       <c r="D44" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E44" s="2">
-        <v>12024</v>
+        <v>13205</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N44" s="8">
-        <v>0.89</v>
+        <v>0.1166</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q44" s="12">
         <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>13.909750000000001</v>
+        <v>13.839</v>
       </c>
       <c r="B45" s="3">
-        <v>-89.493305559999996</v>
+        <v>-88.84783333</v>
       </c>
       <c r="C45" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2">
-        <v>10221</v>
+        <v>12186</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H45" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="J45" s="5" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N45" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>82</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q45" s="12">
         <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>14.02502778</v>
+        <v>13.851000000000001</v>
       </c>
       <c r="B46" s="3">
-        <v>-89.524361110000001</v>
+        <v>-88.907666669999998</v>
       </c>
       <c r="C46" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2">
-        <v>10428</v>
+        <v>12278</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N46" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>82</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q46" s="12">
         <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>13.80019444</v>
+        <v>13.688333330000001</v>
       </c>
       <c r="B47" s="3">
-        <v>-88.154722219999996</v>
+        <v>-88.978611110000003</v>
       </c>
       <c r="C47" s="2">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2">
         <v>3</v>
       </c>
-      <c r="D47" s="2">
-        <v>13</v>
-      </c>
       <c r="E47" s="2">
-        <v>13241</v>
+        <v>11785</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N47" s="8">
-        <v>0.19539999999999999</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q47" s="12">
         <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>13.90694444</v>
+        <v>13.73063889</v>
       </c>
       <c r="B48" s="3">
-        <v>-88.157777780000004</v>
+        <v>-88.887083329999996</v>
       </c>
       <c r="C48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2">
-        <v>13205</v>
+        <v>11873</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N48" s="8">
-        <v>0.1166</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q48" s="12">
         <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>13.839</v>
+        <v>13.93805556</v>
       </c>
       <c r="B49" s="3">
-        <v>-88.84783333</v>
+        <v>-89.028055559999999</v>
       </c>
       <c r="C49" s="2">
         <v>4</v>
       </c>
       <c r="D49" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="2">
-        <v>12186</v>
+        <v>11907</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N49" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q49" s="12">
         <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>13.851000000000001</v>
+        <v>13.87683333</v>
       </c>
       <c r="B50" s="3">
-        <v>-88.907666669999998</v>
+        <v>-89.067722219999993</v>
       </c>
       <c r="C50" s="2">
         <v>4</v>
       </c>
       <c r="D50" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E50" s="2">
-        <v>12278</v>
+        <v>72071</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>132</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>266</v>
+        <v>18</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="N50" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q50" s="12">
         <v>0</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>13.688333330000001</v>
+        <v>13.496111109999999</v>
       </c>
       <c r="B51" s="3">
-        <v>-88.978611110000003</v>
+        <v>-89.030277780000006</v>
       </c>
       <c r="C51" s="2">
         <v>4</v>
       </c>
       <c r="D51" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E51" s="2">
-        <v>11785</v>
+        <v>11926</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="N51" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q51" s="12">
         <v>0</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>13.73063889</v>
+        <v>13.74089225</v>
       </c>
       <c r="B52" s="3">
-        <v>-88.887083329999996</v>
+        <v>-89.427148900000006</v>
       </c>
       <c r="C52" s="2">
         <v>4</v>
       </c>
       <c r="D52" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2">
-        <v>11873</v>
+        <v>11178</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="J52" s="5" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N52" s="8">
-        <v>0</v>
+        <v>3.5299999999999998E-2</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q52" s="12">
         <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>13.93805556</v>
+        <v>13.783611110000001</v>
       </c>
       <c r="B53" s="3">
-        <v>-89.028055559999999</v>
+        <v>-89.330555559999993</v>
       </c>
       <c r="C53" s="2">
         <v>4</v>
       </c>
       <c r="D53" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E53" s="2">
-        <v>11907</v>
+        <v>68123</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="M53" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N53" s="8">
-        <v>1</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q53" s="12">
         <v>0</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>13.87683333</v>
+        <v>13.71555556</v>
       </c>
       <c r="B54" s="3">
-        <v>-89.067722219999993</v>
+        <v>-89.415000000000006</v>
       </c>
       <c r="C54" s="2">
         <v>4</v>
       </c>
       <c r="D54" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E54" s="2">
-        <v>72071</v>
+        <v>68057</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="N54" s="8">
-        <v>1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q54" s="12">
         <v>0</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>13.496111109999999</v>
+        <v>13.942500000000001</v>
       </c>
       <c r="B55" s="3">
-        <v>-89.030277780000006</v>
+        <v>-89.372222219999998</v>
       </c>
       <c r="C55" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2">
-        <v>11926</v>
+        <v>11209</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>141</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="N55" s="8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q55" s="12">
         <v>0</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>13.74089225</v>
+        <v>13.914999999999999</v>
       </c>
       <c r="B56" s="3">
-        <v>-89.427148900000006</v>
+        <v>-89.420555559999997</v>
       </c>
       <c r="C56" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2">
-        <v>11178</v>
+        <v>86408</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N56" s="8">
-        <v>3.5299999999999998E-2</v>
+        <v>0.38</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="12">
         <v>0</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>13.783611110000001</v>
+        <v>13.87833333</v>
       </c>
       <c r="B57" s="3">
-        <v>-89.330555559999993</v>
+        <v>-89.306111110000003</v>
       </c>
       <c r="C57" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E57" s="2">
-        <v>68123</v>
+        <v>68129</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H57" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K57" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="L57" s="2" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N57" s="8">
-        <v>3.6999999999999998E-2</v>
+        <v>0.38</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="12">
         <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>13.71555556</v>
+        <v>13.95975</v>
       </c>
       <c r="B58" s="3">
-        <v>-89.415000000000006</v>
+        <v>-89.544027779999993</v>
       </c>
       <c r="C58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
         <v>4</v>
       </c>
-      <c r="D58" s="2">
-        <v>10</v>
-      </c>
       <c r="E58" s="2">
-        <v>68057</v>
+        <v>10463</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="H58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J58" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>238</v>
-      </c>
       <c r="K58" s="2" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N58" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.38</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="12">
         <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>13.942500000000001</v>
+        <v>13.67111111</v>
       </c>
       <c r="B59" s="3">
-        <v>-89.372222219999998</v>
+        <v>-89.410277780000001</v>
       </c>
       <c r="C59" s="2">
         <v>5</v>
       </c>
       <c r="D59" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>11209</v>
+        <v>11276</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N59" s="8">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="12">
         <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>13.914999999999999</v>
+        <v>13.56875</v>
       </c>
       <c r="B60" s="3">
-        <v>-89.420555559999997</v>
+        <v>-88.343833329999995</v>
       </c>
       <c r="C60" s="2">
         <v>5</v>
       </c>
       <c r="D60" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>86408</v>
+        <v>12907</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N60" s="8">
-        <v>0.38</v>
+        <v>4.99E-2</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="12">
         <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>13.87833333</v>
+        <v>13.53119444</v>
       </c>
       <c r="B61" s="3">
-        <v>-89.306111110000003</v>
+        <v>-88.311527780000006</v>
       </c>
       <c r="C61" s="2">
         <v>5</v>
       </c>
       <c r="D61" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61" s="2">
-        <v>68129</v>
+        <v>12856</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N61" s="8">
-        <v>0.38</v>
+        <v>4.6800000000000001E-2</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="12">
         <v>0</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>13.95975</v>
+        <v>13.47494444</v>
       </c>
       <c r="B62" s="3">
-        <v>-89.544027779999993</v>
+        <v>-88.194611109999997</v>
       </c>
       <c r="C62" s="2">
         <v>5</v>
       </c>
       <c r="D62" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2">
-        <v>10463</v>
+        <v>12991</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="J62" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>108</v>
+        <v>232</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N62" s="8">
-        <v>0.38</v>
+        <v>2.98E-2</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="12">
         <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>13.67111111</v>
+        <v>14.00675</v>
       </c>
       <c r="B63" s="3">
-        <v>-89.410277780000001</v>
+        <v>-89.493472220000001</v>
       </c>
       <c r="C63" s="2">
         <v>5</v>
       </c>
       <c r="D63" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" s="2">
-        <v>11276</v>
+        <v>10452</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="N63" s="8">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="12">
         <v>0</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>13.56875</v>
+        <v>14.14544444</v>
       </c>
       <c r="B64" s="3">
-        <v>-88.343833329999995</v>
+        <v>-89.561472219999999</v>
       </c>
       <c r="C64" s="2">
         <v>5</v>
       </c>
       <c r="D64" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>12907</v>
+        <v>10543</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="I64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J64" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="J64" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="K64" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N64" s="8">
-        <v>4.99E-2</v>
+        <v>0.15</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="12">
         <v>0</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>13.53119444</v>
+        <v>14.043361109999999</v>
       </c>
       <c r="B65" s="3">
-        <v>-88.311527780000006</v>
+        <v>-88.937527779999996</v>
       </c>
       <c r="C65" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D65" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2">
-        <v>12856</v>
+        <v>10797</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N65" s="8">
-        <v>4.6800000000000001E-2</v>
+        <v>0.63</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="12">
         <v>0</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>13.47494444</v>
+        <v>14.315250000000001</v>
       </c>
       <c r="B66" s="3">
-        <v>-88.194611109999997</v>
+        <v>-89.170138890000004</v>
       </c>
       <c r="C66" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2">
-        <v>12991</v>
+        <v>10865</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N66" s="8">
-        <v>2.98E-2</v>
+        <v>0.63</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="12">
         <v>0</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>14.07927778</v>
+        <v>13.510305560000001</v>
       </c>
       <c r="B67" s="3">
-        <v>-89.602777779999997</v>
+        <v>-88.345527779999998</v>
       </c>
       <c r="C67" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D67" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E67" s="2">
-        <v>10183</v>
+        <v>12857</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>266</v>
+        <v>97</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N67" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N67" s="8">
+        <v>0.75</v>
+      </c>
       <c r="O67" s="2" t="s">
         <v>82</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="Q67" s="12">
         <v>0</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>14.00675</v>
+        <v>13.87645</v>
       </c>
       <c r="B68" s="3">
-        <v>-89.493472220000001</v>
+        <v>-88.622866669999993</v>
       </c>
       <c r="C68" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E68" s="2">
-        <v>10452</v>
+        <v>12269</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="N68" s="8">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="Q68" s="12">
         <v>0</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>14.14544444</v>
+        <v>14.02830556</v>
       </c>
       <c r="B69" s="3">
-        <v>-89.561472219999999</v>
+        <v>-89.442138889999995</v>
       </c>
       <c r="C69" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2">
-        <v>10543</v>
+        <v>10444</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N69" s="8">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="Q69" s="12">
         <v>0</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>14.043361109999999</v>
+        <v>14.05119444</v>
       </c>
       <c r="B70" s="3">
-        <v>-88.937527779999996</v>
+        <v>-89.468805560000007</v>
       </c>
       <c r="C70" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E70" s="2">
-        <v>10797</v>
+        <v>10447</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N70" s="8">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q70" s="12">
         <v>0</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>14.315250000000001</v>
+        <v>14.051138890000001</v>
       </c>
       <c r="B71" s="3">
-        <v>-89.170138890000004</v>
+        <v>-89.435305560000003</v>
       </c>
       <c r="C71" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E71" s="2">
-        <v>10865</v>
+        <v>62096</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>179</v>
+        <v>34</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N71" s="8">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q71" s="12">
         <v>0</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>13.510305560000001</v>
+        <v>14.10575</v>
       </c>
       <c r="B72" s="3">
-        <v>-88.345527779999998</v>
+        <v>-89.507833329999997</v>
       </c>
       <c r="C72" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D72" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E72" s="2">
-        <v>12857</v>
+        <v>10527</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>167</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N72" s="8">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q72" s="12">
         <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>13.87645</v>
+        <v>13.94612521</v>
       </c>
       <c r="B73" s="3">
-        <v>-88.622866669999993</v>
+        <v>-89.393292759999994</v>
       </c>
       <c r="C73" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D73" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E73" s="2">
-        <v>12269</v>
+        <v>68118</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>241</v>
+        <v>178</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="N73" s="8">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="Q73" s="12">
         <v>0</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>13.788816669999999</v>
+        <v>13.76616667</v>
       </c>
       <c r="B74" s="3">
-        <v>-88.811666669999994</v>
+        <v>-89.683694439999996</v>
       </c>
       <c r="C74" s="2">
         <v>7</v>
       </c>
       <c r="D74" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E74" s="2">
-        <v>12156</v>
+        <v>64042</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N74" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="N74" s="8">
+        <v>0.81</v>
+      </c>
       <c r="O74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="Q74" s="12">
         <v>0</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>13.89381667</v>
+        <v>13.824583329999999</v>
       </c>
       <c r="B75" s="3">
-        <v>-88.804450000000003</v>
+        <v>-88.807500000000005</v>
       </c>
       <c r="C75" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2">
-        <v>12158</v>
+        <v>12178</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J75" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M75" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K75" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N75" s="8"/>
+      <c r="N75" s="8">
+        <v>1</v>
+      </c>
       <c r="O75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="Q75" s="12">
         <v>0</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>13.95291667</v>
+        <v>13.813416670000001</v>
       </c>
       <c r="B76" s="3">
-        <v>-88.734200000000001</v>
+        <v>-88.794633329999996</v>
       </c>
       <c r="C76" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2">
-        <v>12232</v>
+        <v>12180</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J76" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M76" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N76" s="8"/>
+      <c r="N76" s="8">
+        <v>1</v>
+      </c>
       <c r="O76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="Q76" s="12">
         <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>13.45027778</v>
+        <v>13.62405556</v>
       </c>
       <c r="B77" s="3">
-        <v>-88.222944440000006</v>
+        <v>-89.740722219999995</v>
       </c>
       <c r="C77" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="2">
-        <v>13054</v>
+        <v>64113</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N77" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N77" s="8">
+        <v>0.85</v>
+      </c>
       <c r="O77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="Q77" s="12">
         <v>0</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>13.77605556</v>
+        <v>13.6425</v>
       </c>
       <c r="B78" s="3">
-        <v>-87.892972220000004</v>
+        <v>-89.409166670000005</v>
       </c>
       <c r="C78" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E78" s="2">
-        <v>86015</v>
+        <v>68030</v>
       </c>
       <c r="F78" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I78" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N78" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N78" s="8">
+        <v>0.85</v>
+      </c>
       <c r="O78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="Q78" s="12">
         <v>0</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>13.81208333</v>
+        <v>13.610055559999999</v>
       </c>
       <c r="B79" s="3">
-        <v>-87.950611109999997</v>
+        <v>-88.02416667</v>
       </c>
       <c r="C79" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E79" s="2">
-        <v>84012</v>
+        <v>13218</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N79" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N79" s="8">
+        <v>0.85</v>
+      </c>
       <c r="O79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="Q79" s="12">
         <v>0</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>13.82666667</v>
+        <v>13.94108333</v>
       </c>
       <c r="B80" s="3">
-        <v>-87.96083333</v>
+        <v>-89.619111110000006</v>
       </c>
       <c r="C80" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E80" s="2">
-        <v>84014</v>
+        <v>10462</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>267</v>
+        <v>102</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N80" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N80" s="8">
+        <v>0.85</v>
+      </c>
       <c r="O80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="Q80" s="12">
         <v>0</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>13.786583329999999</v>
+        <v>13.83675</v>
       </c>
       <c r="B81" s="3">
-        <v>-88.050944439999995</v>
+        <v>-87.825083329999998</v>
       </c>
       <c r="C81" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E81" s="2">
-        <v>84119</v>
+        <v>13502</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I81" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N81" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N81" s="8">
+        <v>0.85</v>
+      </c>
       <c r="O81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="Q81" s="12">
         <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>14.02830556</v>
+        <v>13.661944439999999</v>
       </c>
       <c r="B82" s="3">
-        <v>-89.442138889999995</v>
+        <v>-89.371666669999996</v>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E82" s="2">
-        <v>10444</v>
+        <v>11048</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N82" s="8">
         <v>0.85</v>
@@ -5998,33 +5911,33 @@
         <v>10</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="Q82" s="12">
         <v>0</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>14.05119444</v>
+        <v>-89.53197222</v>
       </c>
       <c r="B83" s="3">
-        <v>-89.468805560000007</v>
+        <v>13.967000000000001</v>
       </c>
       <c r="C83" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D83" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E83" s="2">
-        <v>10447</v>
+        <v>10429</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>34</v>
@@ -6033,1230 +5946,1248 @@
         <v>34</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N83" s="8">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q83" s="12">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R83" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>14.051138890000001</v>
+        <v>-89.649722220000001</v>
       </c>
       <c r="B84" s="3">
-        <v>-89.435305560000003</v>
+        <v>14.11238889</v>
       </c>
       <c r="C84" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D84" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E84" s="2">
-        <v>62096</v>
+        <v>10198</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N84" s="8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P84" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q84" s="12">
-        <v>0</v>
-      </c>
-      <c r="R84" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>14.10575</v>
+        <v>-89.675333330000001</v>
       </c>
       <c r="B85" s="3">
-        <v>-89.507833329999997</v>
+        <v>13.98366667</v>
       </c>
       <c r="C85" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D85" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E85" s="2">
-        <v>10527</v>
+        <v>10268</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N85" s="8">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q85" s="12">
-        <v>0</v>
-      </c>
-      <c r="R85" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R85" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>13.94612521</v>
+        <v>-89.559972220000006</v>
       </c>
       <c r="B86" s="3">
-        <v>-89.393292759999994</v>
+        <v>14.10125</v>
       </c>
       <c r="C86" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D86" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E86" s="2">
-        <v>68118</v>
+        <v>10455</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N86" s="8">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P86" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q86" s="12">
-        <v>0</v>
-      </c>
-      <c r="R86" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>13.76616667</v>
+        <v>-89.646249999999995</v>
       </c>
       <c r="B87" s="3">
-        <v>-89.683694439999996</v>
+        <v>13.99775</v>
       </c>
       <c r="C87" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D87" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E87" s="2">
-        <v>64042</v>
+        <v>86287</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>200</v>
+        <v>97</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>266</v>
+        <v>97</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="N87" s="8">
-        <v>0.81</v>
+        <v>0</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q87" s="12">
-        <v>0</v>
-      </c>
-      <c r="R87" s="3" t="s">
-        <v>253</v>
+        <v>82</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>13.824583329999999</v>
+        <v>-89.183611110000001</v>
       </c>
       <c r="B88" s="3">
-        <v>-88.807500000000005</v>
+        <v>13.681944440000001</v>
       </c>
       <c r="C88" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D88" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E88" s="2">
-        <v>12178</v>
+        <v>13242</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>129</v>
+        <v>247</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="N88" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q88" s="12">
-        <v>0</v>
-      </c>
-      <c r="R88" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>13.813416670000001</v>
+        <v>-88.092916669999994</v>
       </c>
       <c r="B89" s="3">
-        <v>-88.794633329999996</v>
+        <v>13.64777778</v>
       </c>
       <c r="C89" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D89" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E89" s="2">
-        <v>12180</v>
+        <v>13249</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>129</v>
+        <v>247</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="N89" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q89" s="12">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>13.911666670000001</v>
+        <v>-87.843944440000001</v>
       </c>
       <c r="B90" s="3">
-        <v>-89.261944439999994</v>
+        <v>13.33897222</v>
       </c>
       <c r="C90" s="2">
+        <v>10</v>
+      </c>
+      <c r="D90" s="2">
         <v>8</v>
       </c>
-      <c r="D90" s="2">
-        <v>3</v>
-      </c>
       <c r="E90" s="2">
-        <v>68098</v>
+        <v>13443</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N90" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N90" s="8">
+        <v>0</v>
+      </c>
       <c r="O90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q90" s="12">
-        <v>0</v>
-      </c>
-      <c r="R90" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R90" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>13.74338889</v>
+        <v>-87.843000000000004</v>
       </c>
       <c r="B91" s="3">
-        <v>-89.637749999999997</v>
+        <v>13.332916669999999</v>
       </c>
       <c r="C91" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E91" s="2">
-        <v>10621</v>
+        <v>13446</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>266</v>
+        <v>97</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N91" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N91" s="8">
+        <v>0</v>
+      </c>
       <c r="O91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q91" s="12">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q91" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>13.752750000000001</v>
+        <v>-87.854277780000004</v>
       </c>
       <c r="B92" s="3">
-        <v>-89.499250000000004</v>
+        <v>13.34055556</v>
       </c>
       <c r="C92" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D92" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E92" s="2">
-        <v>64125</v>
+        <v>10820</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>266</v>
+        <v>97</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N92" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N92" s="8">
+        <v>0</v>
+      </c>
       <c r="O92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q92" s="12">
-        <v>0</v>
-      </c>
-      <c r="R92" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>13.87616667</v>
+        <v>-89.233055559999997</v>
       </c>
       <c r="B93" s="3">
-        <v>-87.839527779999997</v>
+        <v>14.180277780000001</v>
       </c>
       <c r="C93" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D93" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E93" s="2">
-        <v>13459</v>
+        <v>10756</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N93" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N93" s="8">
+        <v>0</v>
+      </c>
       <c r="O93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q93" s="12">
-        <v>0</v>
-      </c>
-      <c r="R93" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>13.51508333</v>
+        <v>-89.293888890000005</v>
       </c>
       <c r="B94" s="3">
-        <v>-88.299611110000001</v>
+        <v>14.123333329999999</v>
       </c>
       <c r="C94" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D94" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E94" s="2">
-        <v>82078</v>
+        <v>10915</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N94" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N94" s="8">
+        <v>0</v>
+      </c>
       <c r="O94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q94" s="12">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R94" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>13.636583330000001</v>
+        <v>-89.180444440000002</v>
       </c>
       <c r="B95" s="3">
-        <v>-89.84530556</v>
+        <v>14.33997222</v>
       </c>
       <c r="C95" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D95" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E95" s="2">
-        <v>10559</v>
+        <v>10949</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N95" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N95" s="8">
+        <v>0</v>
+      </c>
       <c r="O95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q95" s="12">
-        <v>0</v>
-      </c>
-      <c r="R95" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>13.59108333</v>
+        <v>-89.577833330000004</v>
       </c>
       <c r="B96" s="3">
-        <v>-89.826666669999994</v>
+        <v>13.81588889</v>
       </c>
       <c r="C96" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D96" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E96" s="2">
-        <v>10544</v>
+        <v>82062</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N96" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N96" s="8">
+        <v>0</v>
+      </c>
       <c r="O96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q96" s="12">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>13.42733333</v>
+        <v>-88.344305559999995</v>
       </c>
       <c r="B97" s="3">
-        <v>-88.227583330000002</v>
+        <v>13.81497222</v>
       </c>
       <c r="C97" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E97" s="2">
-        <v>13008</v>
+        <v>12975</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N97" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N97" s="8">
+        <v>0</v>
+      </c>
       <c r="O97" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q97" s="12">
-        <v>0</v>
-      </c>
-      <c r="R97" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R97" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>13.696</v>
+        <v>-88.361166670000003</v>
       </c>
       <c r="B98" s="3">
-        <v>-87.867999999999995</v>
+        <v>13.717499999999999</v>
       </c>
       <c r="C98" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D98" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E98" s="2">
-        <v>13332</v>
+        <v>13122</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N98" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="N98" s="8">
+        <v>0</v>
+      </c>
       <c r="O98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q98" s="12">
-        <v>0</v>
-      </c>
-      <c r="R98" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>13.62405556</v>
+        <v>-88.632541669999995</v>
       </c>
       <c r="B99" s="3">
-        <v>-89.740722219999995</v>
+        <v>13.945966670000001</v>
       </c>
       <c r="C99" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D99" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E99" s="2">
-        <v>64113</v>
+        <v>12294</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N99" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q99" s="12">
-        <v>0</v>
-      </c>
-      <c r="R99" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>13.6425</v>
+        <v>-89.297777780000004</v>
       </c>
       <c r="B100" s="3">
-        <v>-89.409166670000005</v>
+        <v>13.53055556</v>
       </c>
       <c r="C100" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E100" s="2">
-        <v>68030</v>
+        <v>11095</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>223</v>
+        <v>72</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N100" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q100" s="12">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R100" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>13.610055559999999</v>
+        <v>-89.518611109999995</v>
       </c>
       <c r="B101" s="3">
-        <v>-88.02416667</v>
+        <v>13.59055556</v>
       </c>
       <c r="C101" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D101" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E101" s="2">
-        <v>13218</v>
+        <v>11284</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>266</v>
+        <v>97</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N101" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q101" s="12">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q101" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>13.94108333</v>
+        <v>-89.122777780000007</v>
       </c>
       <c r="B102" s="3">
-        <v>-89.619111110000006</v>
+        <v>13.598055560000001</v>
       </c>
       <c r="C102" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D102" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E102" s="2">
-        <v>10462</v>
+        <v>10084</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M102" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N102" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q102" s="12">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q102" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>13.83675</v>
+        <v>-88.916555560000006</v>
       </c>
       <c r="B103" s="3">
-        <v>-87.825083329999998</v>
+        <v>13.305944439999999</v>
       </c>
       <c r="C103" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E103" s="2">
-        <v>13502</v>
+        <v>12132</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N103" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P103" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q103" s="12">
-        <v>0</v>
-      </c>
-      <c r="R103" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>13.661944439999999</v>
+        <v>-88.913055560000004</v>
       </c>
       <c r="B104" s="3">
-        <v>-89.371666669999996</v>
+        <v>13.75111111</v>
       </c>
       <c r="C104" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D104" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E104" s="2">
-        <v>11048</v>
+        <v>11816</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>229</v>
+        <v>274</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>72</v>
+        <v>275</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M104" s="2" t="s">
         <v>81</v>
       </c>
       <c r="N104" s="8">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P104" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q104" s="12">
-        <v>0</v>
-      </c>
-      <c r="R104" s="3" t="s">
-        <v>255</v>
+        <v>82</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R104" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>-89.53197222</v>
+        <v>-88.869229869999998</v>
       </c>
       <c r="B105" s="3">
-        <v>13.967000000000001</v>
+        <v>13.50435055</v>
       </c>
       <c r="C105" s="2">
         <v>10</v>
       </c>
       <c r="D105" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E105" s="2">
-        <v>10429</v>
+        <v>12116</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>81</v>
@@ -7279,40 +7210,40 @@
     </row>
     <row r="106" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>-89.649722220000001</v>
+        <v>-88.856166669999993</v>
       </c>
       <c r="B106" s="3">
-        <v>14.11238889</v>
+        <v>13.84333333</v>
       </c>
       <c r="C106" s="2">
         <v>10</v>
       </c>
       <c r="D106" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E106" s="2">
-        <v>10198</v>
+        <v>12157</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>275</v>
+        <v>124</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>81</v>
@@ -7335,40 +7266,40 @@
     </row>
     <row r="107" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>-89.675333330000001</v>
+        <v>-88.884027779999997</v>
       </c>
       <c r="B107" s="3">
-        <v>13.98366667</v>
+        <v>13.455083330000001</v>
       </c>
       <c r="C107" s="2">
         <v>10</v>
       </c>
       <c r="D107" s="2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E107" s="2">
-        <v>10268</v>
+        <v>12115</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>81</v>
@@ -7386,1238 +7317,6 @@
         <v>82</v>
       </c>
       <c r="R107" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
-        <v>-89.559972220000006</v>
-      </c>
-      <c r="B108" s="3">
-        <v>14.10125</v>
-      </c>
-      <c r="C108" s="2">
-        <v>10</v>
-      </c>
-      <c r="D108" s="2">
-        <v>4</v>
-      </c>
-      <c r="E108" s="2">
-        <v>10455</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L108" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N108" s="8">
-        <v>0</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P108" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R108" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
-        <v>-89.646249999999995</v>
-      </c>
-      <c r="B109" s="3">
-        <v>13.99775</v>
-      </c>
-      <c r="C109" s="2">
-        <v>10</v>
-      </c>
-      <c r="D109" s="2">
-        <v>5</v>
-      </c>
-      <c r="E109" s="2">
-        <v>86287</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L109" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M109" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N109" s="8">
-        <v>0</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P109" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R109" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
-        <v>-89.183611110000001</v>
-      </c>
-      <c r="B110" s="3">
-        <v>13.681944440000001</v>
-      </c>
-      <c r="C110" s="2">
-        <v>10</v>
-      </c>
-      <c r="D110" s="2">
-        <v>6</v>
-      </c>
-      <c r="E110" s="2">
-        <v>13242</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M110" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N110" s="8">
-        <v>0</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R110" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
-        <v>-88.092916669999994</v>
-      </c>
-      <c r="B111" s="3">
-        <v>13.64777778</v>
-      </c>
-      <c r="C111" s="2">
-        <v>10</v>
-      </c>
-      <c r="D111" s="2">
-        <v>7</v>
-      </c>
-      <c r="E111" s="2">
-        <v>13249</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M111" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N111" s="8">
-        <v>0</v>
-      </c>
-      <c r="O111" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P111" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R111" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
-        <v>-87.843944440000001</v>
-      </c>
-      <c r="B112" s="3">
-        <v>13.33897222</v>
-      </c>
-      <c r="C112" s="2">
-        <v>10</v>
-      </c>
-      <c r="D112" s="2">
-        <v>8</v>
-      </c>
-      <c r="E112" s="2">
-        <v>13443</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N112" s="8">
-        <v>0</v>
-      </c>
-      <c r="O112" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P112" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R112" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
-        <v>-87.843000000000004</v>
-      </c>
-      <c r="B113" s="3">
-        <v>13.332916669999999</v>
-      </c>
-      <c r="C113" s="2">
-        <v>10</v>
-      </c>
-      <c r="D113" s="2">
-        <v>9</v>
-      </c>
-      <c r="E113" s="2">
-        <v>13446</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J113" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M113" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N113" s="8">
-        <v>0</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P113" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R113" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
-        <v>-87.854277780000004</v>
-      </c>
-      <c r="B114" s="3">
-        <v>13.34055556</v>
-      </c>
-      <c r="C114" s="2">
-        <v>10</v>
-      </c>
-      <c r="D114" s="2">
-        <v>10</v>
-      </c>
-      <c r="E114" s="2">
-        <v>10820</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L114" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M114" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N114" s="8">
-        <v>0</v>
-      </c>
-      <c r="O114" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P114" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R114" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
-        <v>-89.233055559999997</v>
-      </c>
-      <c r="B115" s="3">
-        <v>14.180277780000001</v>
-      </c>
-      <c r="C115" s="2">
-        <v>10</v>
-      </c>
-      <c r="D115" s="2">
-        <v>11</v>
-      </c>
-      <c r="E115" s="2">
-        <v>10756</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N115" s="8">
-        <v>0</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P115" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R115" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
-        <v>-89.293888890000005</v>
-      </c>
-      <c r="B116" s="3">
-        <v>14.123333329999999</v>
-      </c>
-      <c r="C116" s="2">
-        <v>10</v>
-      </c>
-      <c r="D116" s="2">
-        <v>12</v>
-      </c>
-      <c r="E116" s="2">
-        <v>10915</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J116" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N116" s="8">
-        <v>0</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P116" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R116" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
-        <v>-89.180444440000002</v>
-      </c>
-      <c r="B117" s="3">
-        <v>14.33997222</v>
-      </c>
-      <c r="C117" s="2">
-        <v>10</v>
-      </c>
-      <c r="D117" s="2">
-        <v>13</v>
-      </c>
-      <c r="E117" s="2">
-        <v>10949</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M117" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N117" s="8">
-        <v>0</v>
-      </c>
-      <c r="O117" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P117" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R117" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
-        <v>-89.577833330000004</v>
-      </c>
-      <c r="B118" s="3">
-        <v>13.81588889</v>
-      </c>
-      <c r="C118" s="2">
-        <v>10</v>
-      </c>
-      <c r="D118" s="2">
-        <v>14</v>
-      </c>
-      <c r="E118" s="2">
-        <v>82062</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M118" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N118" s="8">
-        <v>0</v>
-      </c>
-      <c r="O118" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P118" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R118" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
-        <v>-88.344305559999995</v>
-      </c>
-      <c r="B119" s="3">
-        <v>13.81497222</v>
-      </c>
-      <c r="C119" s="2">
-        <v>10</v>
-      </c>
-      <c r="D119" s="2">
-        <v>15</v>
-      </c>
-      <c r="E119" s="2">
-        <v>12975</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M119" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N119" s="8">
-        <v>0</v>
-      </c>
-      <c r="O119" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P119" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R119" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>-88.361166670000003</v>
-      </c>
-      <c r="B120" s="3">
-        <v>13.717499999999999</v>
-      </c>
-      <c r="C120" s="2">
-        <v>10</v>
-      </c>
-      <c r="D120" s="2">
-        <v>16</v>
-      </c>
-      <c r="E120" s="2">
-        <v>13122</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M120" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N120" s="8">
-        <v>0</v>
-      </c>
-      <c r="O120" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P120" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R120" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
-        <v>-88.632541669999995</v>
-      </c>
-      <c r="B121" s="3">
-        <v>13.945966670000001</v>
-      </c>
-      <c r="C121" s="2">
-        <v>10</v>
-      </c>
-      <c r="D121" s="2">
-        <v>17</v>
-      </c>
-      <c r="E121" s="2">
-        <v>12294</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L121" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M121" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N121" s="8">
-        <v>0</v>
-      </c>
-      <c r="O121" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P121" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R121" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>-89.297777780000004</v>
-      </c>
-      <c r="B122" s="3">
-        <v>13.53055556</v>
-      </c>
-      <c r="C122" s="2">
-        <v>10</v>
-      </c>
-      <c r="D122" s="2">
-        <v>18</v>
-      </c>
-      <c r="E122" s="2">
-        <v>11095</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N122" s="8">
-        <v>0</v>
-      </c>
-      <c r="O122" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P122" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R122" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
-        <v>-89.518611109999995</v>
-      </c>
-      <c r="B123" s="3">
-        <v>13.59055556</v>
-      </c>
-      <c r="C123" s="2">
-        <v>10</v>
-      </c>
-      <c r="D123" s="2">
-        <v>19</v>
-      </c>
-      <c r="E123" s="2">
-        <v>11284</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M123" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N123" s="8">
-        <v>0</v>
-      </c>
-      <c r="O123" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P123" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R123" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
-        <v>-89.122777780000007</v>
-      </c>
-      <c r="B124" s="3">
-        <v>13.598055560000001</v>
-      </c>
-      <c r="C124" s="2">
-        <v>10</v>
-      </c>
-      <c r="D124" s="2">
-        <v>20</v>
-      </c>
-      <c r="E124" s="2">
-        <v>10084</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M124" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N124" s="8">
-        <v>0</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P124" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q124" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R124" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
-        <v>-88.916555560000006</v>
-      </c>
-      <c r="B125" s="3">
-        <v>13.305944439999999</v>
-      </c>
-      <c r="C125" s="2">
-        <v>10</v>
-      </c>
-      <c r="D125" s="2">
-        <v>21</v>
-      </c>
-      <c r="E125" s="2">
-        <v>12132</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J125" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N125" s="8">
-        <v>0</v>
-      </c>
-      <c r="O125" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P125" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q125" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R125" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
-        <v>-88.913055560000004</v>
-      </c>
-      <c r="B126" s="3">
-        <v>13.75111111</v>
-      </c>
-      <c r="C126" s="2">
-        <v>10</v>
-      </c>
-      <c r="D126" s="2">
-        <v>22</v>
-      </c>
-      <c r="E126" s="2">
-        <v>11816</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J126" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M126" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N126" s="8">
-        <v>0</v>
-      </c>
-      <c r="O126" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P126" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q126" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R126" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
-        <v>-88.869229869999998</v>
-      </c>
-      <c r="B127" s="3">
-        <v>13.50435055</v>
-      </c>
-      <c r="C127" s="2">
-        <v>10</v>
-      </c>
-      <c r="D127" s="2">
-        <v>23</v>
-      </c>
-      <c r="E127" s="2">
-        <v>12116</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J127" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K127" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M127" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N127" s="8">
-        <v>0</v>
-      </c>
-      <c r="O127" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P127" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q127" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R127" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
-        <v>-88.856166669999993</v>
-      </c>
-      <c r="B128" s="3">
-        <v>13.84333333</v>
-      </c>
-      <c r="C128" s="2">
-        <v>10</v>
-      </c>
-      <c r="D128" s="2">
-        <v>24</v>
-      </c>
-      <c r="E128" s="2">
-        <v>12157</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J128" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M128" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N128" s="8">
-        <v>0</v>
-      </c>
-      <c r="O128" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P128" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q128" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R128" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="3">
-        <v>-88.884027779999997</v>
-      </c>
-      <c r="B129" s="3">
-        <v>13.455083330000001</v>
-      </c>
-      <c r="C129" s="2">
-        <v>10</v>
-      </c>
-      <c r="D129" s="2">
-        <v>25</v>
-      </c>
-      <c r="E129" s="2">
-        <v>12115</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J129" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L129" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M129" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N129" s="8">
-        <v>0</v>
-      </c>
-      <c r="O129" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P129" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q129" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R129" s="2" t="s">
         <v>82</v>
       </c>
     </row>
